--- a/printing/regression/training_error_results_0.6_0.9.xlsx
+++ b/printing/regression/training_error_results_0.6_0.9.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cchih\Desktop\NTHU\MasterThesis\GA\SGM_GA\printing\regression\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB1C512-F0F0-4389-A2D8-2AF7463AC45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75CA95CB-E411-4B0E-BEB0-AE3BF2051525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Training_Error_Details" sheetId="1" r:id="rId1"/>
@@ -594,10 +594,10 @@
       <c r="F2">
         <v>75</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>0.48351229911538041</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="2">
         <v>0.48351229923836792</v>
       </c>
       <c r="I2">
@@ -641,10 +641,10 @@
       <c r="F3">
         <v>59.999999999999993</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>0.45901662751675459</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="2">
         <v>0.45901662791072961</v>
       </c>
       <c r="I3">
@@ -688,10 +688,10 @@
       <c r="F4">
         <v>44.999999999999993</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>0.43973557039816641</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>0.4301893654955346</v>
       </c>
       <c r="I4">
@@ -735,10 +735,10 @@
       <c r="F5">
         <v>111.7380338002902</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <v>0.62929802668878232</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>0.62929802329972417</v>
       </c>
       <c r="I5">
@@ -782,10 +782,10 @@
       <c r="F6">
         <v>79.106605350869103</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="2">
         <v>0.68703573164592169</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="2">
         <v>0.6870357303569159</v>
       </c>
       <c r="I6">
@@ -829,10 +829,10 @@
       <c r="F7">
         <v>56.309932474020208</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="2">
         <v>0.64949988963032212</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="2">
         <v>0.65873291295036229</v>
       </c>
       <c r="I7">
@@ -876,10 +876,10 @@
       <c r="F8">
         <v>38.261966199709839</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="2">
         <v>0.54380155735576474</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="2">
         <v>0.54380155785620399</v>
       </c>
       <c r="I8">
@@ -923,10 +923,10 @@
       <c r="F9">
         <v>40.893394649130897</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="2">
         <v>0.52749718423651881</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="2">
         <v>0.52749718057199269</v>
       </c>
       <c r="I9">
@@ -970,10 +970,10 @@
       <c r="F10">
         <v>33.690067525979792</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="2">
         <v>0.49241198817111898</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="2">
         <v>0.49505443498135687</v>
       </c>
       <c r="I10">
@@ -1017,10 +1017,10 @@
       <c r="F11">
         <v>74.999999999999986</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="2">
         <v>0.79149877345561148</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="2">
         <v>0.79149877501792776</v>
       </c>
       <c r="I11">
@@ -1064,10 +1064,10 @@
       <c r="F12">
         <v>60.000000000000007</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="2">
         <v>0.77814030586794569</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="2">
         <v>0.77814031298015207</v>
       </c>
       <c r="I12">
@@ -1111,10 +1111,10 @@
       <c r="F13">
         <v>45.000000000000021</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="2">
         <v>0.74563354580372954</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="2">
         <v>0.74537143275779016</v>
       </c>
       <c r="I13">
